--- a/Template_HRC_Farmatodo.xlsx
+++ b/Template_HRC_Farmatodo.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +30,37 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00002366"/>
+        <bgColor rgb="00002366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E90FF"/>
+        <bgColor rgb="001E90FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,24 +81,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -448,81 +478,89 @@
           <t>Desglose de Pago</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>REFERENCIA DE PAGO</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>10000061418</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>CAMPOS NO EDITABLES</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>FARMATODO COLOMBIA S A</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>TOTAL s/ BANCOS</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
-      <c r="F7" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>TOTAL s/ DETALLE</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="4" t="n">
+        <v>0.4399999901652336</v>
+      </c>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Codigo de Cliente</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>10324901</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>DIFERENCIA</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="4" t="n">
+        <v>0.5600000098347664</v>
+      </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Método de Pago</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -532,801 +570,790 @@
       <c r="C12" t="n">
         <v>10000061418</v>
       </c>
+      <c r="D12" s="5" t="n">
+        <v>45904</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n"/>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Tipo de Documento</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Referencia / Factura</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Importe de factura</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Descuento</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Motivo del descuento</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Pago Neto</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Comentarios</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Factura</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>PMP1257526</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="10" t="n">
         <v>8933837.32</v>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="2" t="n">
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="10" t="n">
         <v>8933837.32</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>PMP1257526 OC:14002950 UNILEVER ANDINA COLOMBIA LTDA</t>
-        </is>
-      </c>
+      <c r="I19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Factura</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>PMP1257525</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="10" t="n">
         <v>4062750.96</v>
       </c>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="2" t="n">
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="10" t="n">
         <v>4062750.96</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>PMP1257525 OC:14002954 UNILEVER ANDINA COLOMBIA LTDA</t>
-        </is>
-      </c>
+      <c r="I20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Factura</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>PMP1257523</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="10" t="n">
         <v>22044554.27</v>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="2" t="n">
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="10" t="n">
         <v>22044554.27</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>PMP1257523 OC:14002950 UNILEVER ANDINA COLOMBIA LTDA</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Factura</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>PMP1254823</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="10" t="n">
         <v>120905183.36</v>
       </c>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="2" t="n">
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="10" t="n">
         <v>120905183.36</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>PMP1254823 OC:14002465 UNILEVER ANDINA COLOMBIA LTDA</t>
-        </is>
-      </c>
+      <c r="I22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>FV-XKZV26513</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="10" t="n">
         <v>-811023.46</v>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>FACT PROVEEDOR</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>CSB</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="10" t="n">
         <v>-811023.46</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>FV-XKZV26513 Acuerdo Fijo Mensual 01 7%� - MASIVOS/MISCELANEOS Exhibiciones Adicionales</t>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR FV-XKZV26513 Acuerdo Fijo Mensual 01 7%� - MASIVOS/MISCELANEOS Exhibiciones Adicionales</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>FV-XKZV27008</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="10" t="n">
         <v>-15470000</v>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>FACT PROVEEDOR</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>CSB</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="10" t="n">
         <v>-15470000</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>FV-XKZV27008 Cobro Descuento Apoyo Apertura mes de Junio-2025 Masivos Sucursal</t>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>FACT PROVEEDOR FV-XKZV27008 Cobro Descuento Apoyo Apertura mes de Junio-2025 Masivos Sucursal</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>NC-PMP1257525</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="10" t="n">
         <v>-68281.53</v>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>DSCT AVERIAS</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="10" t="n">
         <v>-68281.53</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>NC-PMP1257525 OC:14004661 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>DSCT AVERIAS NC-PMP1257525 OC:14004661 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>NC-PMP1257523</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="10" t="n">
         <v>-370496.71</v>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>DSCT AVERIAS</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="10" t="n">
         <v>-370496.71</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>NC-PMP1257523 OC:14004661 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>DSCT AVERIAS NC-PMP1257523 OC:14004661 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>NCF-DC05-16088</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="10" t="n">
         <v>-13948980.1</v>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>CONVENIOS</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="10" t="n">
         <v>-13948980.1</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>NCF-DC05-16088 Confidencial Acuerdo Fijo Mensual .4% 01-06-2025-30-06-20</t>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>CONVENIOS NCF-DC05-16088 Confidencial Acuerdo Fijo Mensual .4% 01-06-2025-30-06-20</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>NC100320204</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="10" t="n">
         <v>-1487731.61</v>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>DSCT AVERIAS</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>522</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="10" t="n">
         <v>-1487731.61</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>NC100320204 NOTAS DE CREDITO POR DEVOLUCION 100320204</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>DSCT AVERIAS NC100320204 NOTAS DE CREDITO POR DEVOLUCION 100320204</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755525</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="10" t="n">
         <v>-165487</v>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="10" t="n">
         <v>-165487</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755525 Liquidaciones Ventas Pos -Primera Compra Junio - Belleza y cuidado personal</t>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755525 Liquidaciones Ventas Pos -Primera Compra Junio - Belleza y cuidado personal</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755523</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="10" t="n">
         <v>-1183970.05</v>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="10" t="n">
         <v>-1183970.05</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755523 Liquidaciones Ventas Pos -72 Horas 13 al 15 Junio - Belleza y cuidado personal</t>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755523 Liquidaciones Ventas Pos -72 Horas 13 al 15 Junio - Belleza y cuidado personal</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755521</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="10" t="n">
         <v>-2473742.3</v>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="10" t="n">
         <v>-2473742.3</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755521 Liquidaciones Ventas Pos -Folleto Quincenal 6 al 19 Junio - Belleza y cuidado personal</t>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755521 Liquidaciones Ventas Pos -Folleto Quincenal 6 al 19 Junio - Belleza y cuidado personal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755517</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="10" t="n">
         <v>-964465.5</v>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="10" t="n">
         <v>-964465.5</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755517 Liquidaciones ventas pos junio - Dcto Feria General</t>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755517 Liquidaciones ventas pos junio - Dcto Feria General</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755515</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="10" t="n">
         <v>-1563430</v>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="10" t="n">
         <v>-1563430</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755515 Liquidaciones ventas pos junio - Folleto 23 a 5</t>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755515 Liquidaciones ventas pos junio - Folleto 23 a 5</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755513</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="10" t="n">
         <v>-8138292.12</v>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="10" t="n">
         <v>-8138292.12</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755513 Liquidaciones Ventas Pos -Combos Virtuales Junio - Belleza y cuidado personal</t>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755513 Liquidaciones Ventas Pos -Combos Virtuales Junio - Belleza y cuidado personal</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755512</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="10" t="n">
         <v>-13029314.1</v>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="10" t="n">
         <v>-13029314.1</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755512 Liquidaciones Ventas Pos -Descuento Feria 12 al 15 Junio - Belleza y cuidado personal</t>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755512 Liquidaciones Ventas Pos -Descuento Feria 12 al 15 Junio - Belleza y cuidado personal</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755511</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="10" t="n">
         <v>-15374384.45</v>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="10" t="n">
         <v>-15374384.45</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755511 Liquidaciones ventas pos junio - Primaton</t>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755511 Liquidaciones ventas pos junio - Primaton</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>NC-DC04-755509</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="10" t="n">
         <v>-36331344.8</v>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>DSCT PROMOCIONAL</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="10" t="n">
         <v>-36331344.8</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>NC-DC04-755509 Liquidaciones Ventas Pos -Primera Compra Junio - Belleza y cuidado personal</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>DSCT PROMOCIONAL NC-DC04-755509 Liquidaciones Ventas Pos -Primera Compra Junio - Belleza y cuidado personal</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>NC-PMP1257526</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="10" t="n">
         <v>-150148.53</v>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>DSCT AVERIAS</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="10" t="n">
         <v>-150148.53</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>NC-PMP1257526 OC:14004661 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>DSCT AVERIAS NC-PMP1257526 OC:14004661 UNILEVER ANDINA COLOMBIA LTDA (DPP)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>PMP1257525</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="10" t="n">
         <v>-0.5200000000186265</v>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>WOB</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="10" t="n">
         <v>-0.5200000000186265</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>PMP1257523</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>384</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>PMP1254823</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="10" t="n">
         <v>0.06000000238418579</v>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>384</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="10" t="n">
         <v>0.06000000238418579</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Nota de Crédito</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>1200010915</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="10" t="n">
         <v>-44415234</v>
       </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>NRO</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="10" t="n">
         <v>-44415234</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>Pendiente de Aplicar sin Soporte</t>
         </is>

--- a/Template_HRC_Farmatodo.xlsx
+++ b/Template_HRC_Farmatodo.xlsx
@@ -469,9 +469,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:I42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="120" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
@@ -487,6 +499,7 @@
         <v>10000061418</v>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -494,6 +507,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -544,6 +558,8 @@
         <v>0.5600000098347664</v>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -571,7 +587,7 @@
         <v>10000061418</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -582,6 +598,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="C18" s="6" t="inlineStr">
         <is>
